--- a/resource/test_map.xlsx
+++ b/resource/test_map.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="52">
   <si>
     <t>0
 1345</t>
@@ -426,7 +426,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -513,24 +513,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -616,12 +604,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -848,70 +830,70 @@
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1829,8 +1811,12 @@
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+      <c r="E7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="G7" s="4" t="s">
         <v>24</v>
       </c>
@@ -1889,8 +1875,12 @@
       <c r="D8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="G8" s="4" t="s">
         <v>24</v>
       </c>

--- a/resource/test_map.xlsx
+++ b/resource/test_map.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="51">
   <si>
     <t>0
 1345</t>
@@ -181,9 +181,6 @@
     <t>9
 1232
 5深位</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  上下货</t>
   </si>
   <si>
     <t>上货</t>
@@ -2081,25 +2078,25 @@
         <v>24</v>
       </c>
       <c r="J11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="L11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>24</v>
@@ -2122,7 +2119,7 @@
     </row>
     <row r="12" ht="33" customHeight="1" spans="1:22">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -2146,22 +2143,22 @@
         <v>24</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q12" s="4" t="s">
         <v>24</v>
@@ -2184,7 +2181,7 @@
     </row>
     <row r="13" ht="33" customHeight="1" spans="1:22">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -2246,7 +2243,7 @@
     </row>
     <row r="14" ht="33" customHeight="1" spans="1:22">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>22</v>
@@ -2314,7 +2311,7 @@
     </row>
     <row r="15" ht="33" customHeight="1" spans="1:22">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>24</v>
@@ -2382,7 +2379,7 @@
     </row>
     <row r="16" ht="33" customHeight="1" spans="1:22">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>32</v>
@@ -2450,7 +2447,7 @@
     </row>
     <row r="17" ht="33" customHeight="1" spans="1:22">
       <c r="A17" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>24</v>
@@ -2504,7 +2501,7 @@
         <v>35</v>
       </c>
       <c r="S17" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T17" s="5" t="s">
         <v>35</v>
@@ -2518,7 +2515,7 @@
     </row>
     <row r="18" ht="33" customHeight="1" spans="1:22">
       <c r="A18" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>24</v>
@@ -2580,7 +2577,7 @@
     </row>
     <row r="19" ht="33" customHeight="1" spans="1:22">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>24</v>
@@ -2642,7 +2639,7 @@
     </row>
     <row r="20" ht="33" customHeight="1" spans="1:22">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>24</v>
@@ -2704,7 +2701,7 @@
     </row>
     <row r="21" ht="33" customHeight="1" spans="1:22">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>24</v>
@@ -2766,64 +2763,64 @@
     </row>
     <row r="22" ht="33" customHeight="1" spans="1:22">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
       <c r="U22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="V22" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
